--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0003T0006Z000C1N23_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0003T0006Z000C1N23_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>39.51284788467458</v>
+        <v>6.42083778125962</v>
       </c>
       <c r="D2" t="n">
-        <v>38.96834240733101</v>
+        <v>6.33235564119129</v>
       </c>
       <c r="E2" t="n">
-        <v>12.1199322847279</v>
+        <v>1.969488996268284</v>
       </c>
       <c r="F2" t="n">
-        <v>11.75449409350605</v>
+        <v>1.910105290194733</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23.0811773794484</v>
+        <v>3.750691324160365</v>
       </c>
       <c r="D3" t="n">
-        <v>24.45874947701622</v>
+        <v>3.974546790015135</v>
       </c>
       <c r="E3" t="n">
-        <v>12.1199322847279</v>
+        <v>1.969488996268284</v>
       </c>
       <c r="F3" t="n">
-        <v>11.75449409350605</v>
+        <v>1.910105290194733</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>8.947113247343006</v>
+        <v>1.453905902693239</v>
       </c>
       <c r="D4" t="n">
-        <v>9.849217818440593</v>
+        <v>1.600497895496596</v>
       </c>
       <c r="E4" t="n">
-        <v>12.1199322847279</v>
+        <v>1.969488996268284</v>
       </c>
       <c r="F4" t="n">
-        <v>11.75449409350605</v>
+        <v>1.910105290194733</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>11.22119254242116</v>
+        <v>1.823443788143439</v>
       </c>
       <c r="D5" t="n">
-        <v>11.32535246911209</v>
+        <v>1.840369776230715</v>
       </c>
       <c r="E5" t="n">
-        <v>12.1199322847279</v>
+        <v>1.969488996268284</v>
       </c>
       <c r="F5" t="n">
-        <v>11.75449409350605</v>
+        <v>1.910105290194733</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
